--- a/data/trans_camb/MCS12_SP_R3-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/MCS12_SP_R3-Habitat-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población en el primer cuartil de la puntuación del componente de salud mental (SF12)</t>
+          <t>Población en el primer cuartil (48.388) de la puntuación del componente de salud mental (SF12)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,36; 9,56</t>
+          <t>2,46; 10,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,17; 7,96</t>
+          <t>0,02; 8,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,58; 10,24</t>
+          <t>2,66; 10,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,04; 18,54</t>
+          <t>9,54; 18,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,19; 11,14</t>
+          <t>2,58; 11,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,45; 8,51</t>
+          <t>0,43; 8,63</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,73; 12,79</t>
+          <t>6,9; 12,92</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,54; 8,64</t>
+          <t>2,58; 8,41</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,72; 8,36</t>
+          <t>2,38; 8,42</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14,44; 75,83</t>
+          <t>14,27; 82,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,97; 65,03</t>
+          <t>-0,94; 64,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,0; 84,08</t>
+          <t>16,42; 85,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39,77; 101,03</t>
+          <t>41,9; 102,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,77; 60,73</t>
+          <t>11,2; 62,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,82; 46,48</t>
+          <t>1,44; 46,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,13; 79,43</t>
+          <t>36,15; 81,63</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>13,72; 54,79</t>
+          <t>13,77; 52,55</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,66; 53,66</t>
+          <t>12,82; 53,15</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 7,39</t>
+          <t>-0,62; 7,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,9; 0,27</t>
+          <t>-6,96; 0,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,92; -0,06</t>
+          <t>-13,44; -0,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 6,17</t>
+          <t>-2,06; 6,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,23; -0,71</t>
+          <t>-8,63; -1,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 1,86</t>
+          <t>-5,51; 2,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 5,48</t>
+          <t>-0,06; 5,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,94; -1,58</t>
+          <t>-6,74; -1,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-12,08; -0,7</t>
+          <t>-11,17; -0,47</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 43,15</t>
+          <t>-3,0; 41,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-31,76; 1,46</t>
+          <t>-32,16; 1,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-63,17; 0,05</t>
+          <t>-63,45; -1,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,38; 22,87</t>
+          <t>-6,58; 23,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-28,42; -2,3</t>
+          <t>-27,71; -3,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-17,67; 6,92</t>
+          <t>-17,16; 9,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 23,42</t>
+          <t>-0,19; 25,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-26,53; -6,83</t>
+          <t>-25,77; -5,79</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-47,39; -2,91</t>
+          <t>-44,97; -2,01</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 7,08</t>
+          <t>-1,05; 7,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 5,06</t>
+          <t>-2,72; 5,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 8,85</t>
+          <t>-0,38; 9,27</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 9,79</t>
+          <t>0,17; 9,66</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 5,06</t>
+          <t>-3,86; 5,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 42,46</t>
+          <t>-2,41; 45,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,81; 7,28</t>
+          <t>1,04; 7,49</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 4,17</t>
+          <t>-2,11; 4,04</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,32; 34,09</t>
+          <t>0,94; 36,13</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 46,42</t>
+          <t>-5,55; 49,55</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-15,44; 34,07</t>
+          <t>-13,98; 35,4</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 57,89</t>
+          <t>-2,13; 58,9</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 41,33</t>
+          <t>0,12; 40,57</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-14,8; 21,11</t>
+          <t>-13,8; 22,35</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-8,17; 175,07</t>
+          <t>-9,26; 180,6</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,78; 37,09</t>
+          <t>4,67; 37,21</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-8,85; 21,27</t>
+          <t>-9,22; 20,05</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,39; 161,29</t>
+          <t>4,45; 179,78</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 6,65</t>
+          <t>-1,13; 6,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 4,08</t>
+          <t>-3,47; 4,04</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 1,67</t>
+          <t>-6,07; 1,33</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,91; 9,89</t>
+          <t>1,83; 10,18</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 4,42</t>
+          <t>-3,12; 4,89</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,93; 3,58</t>
+          <t>-6,55; 3,81</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,46; 7,21</t>
+          <t>1,76; 7,31</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 3,12</t>
+          <t>-2,63; 3,15</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 1,43</t>
+          <t>-4,47; 1,8</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 32,53</t>
+          <t>-4,52; 33,38</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-14,91; 20,91</t>
+          <t>-14,14; 20,17</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-25,35; 8,16</t>
+          <t>-25,47; 6,58</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6,58; 38,15</t>
+          <t>5,55; 38,67</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-11,43; 17,52</t>
+          <t>-10,6; 19,25</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-22,86; 13,39</t>
+          <t>-21,98; 14,23</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,27; 29,86</t>
+          <t>6,68; 31,01</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-10,13; 13,02</t>
+          <t>-9,82; 13,25</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-17,7; 5,86</t>
+          <t>-16,99; 7,5</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,43; 5,63</t>
+          <t>1,68; 5,75</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 2,2</t>
+          <t>-1,66; 2,25</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 2,07</t>
+          <t>-5,14; 2,21</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,88; 8,51</t>
+          <t>3,86; 8,42</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 2,46</t>
+          <t>-1,8; 2,43</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 17,54</t>
+          <t>-0,4; 18,28</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,34; 6,43</t>
+          <t>3,38; 6,37</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 1,66</t>
+          <t>-1,27; 1,61</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 9,47</t>
+          <t>-1,02; 10,09</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>7,09; 31,83</t>
+          <t>8,72; 32,61</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-8,89; 12,62</t>
+          <t>-8,52; 12,76</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-23,33; 11,61</t>
+          <t>-26,14; 12,46</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>13,78; 33,52</t>
+          <t>13,92; 32,96</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-7,27; 9,84</t>
+          <t>-6,51; 9,52</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 71,67</t>
+          <t>-1,51; 72,14</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,31; 29,76</t>
+          <t>14,34; 29,08</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 7,66</t>
+          <t>-5,38; 7,45</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 42,23</t>
+          <t>-4,51; 45,74</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/MCS12_SP_R3-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/MCS12_SP_R3-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6,35</t>
+          <t>6,5</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,62</t>
+          <t>4,56</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5,57</t>
+          <t>5,61</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,46; 10,09</t>
+          <t>1,89; 9,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,02; 8,13</t>
+          <t>0,26; 8,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,66; 10,54</t>
+          <t>2,31; 10,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,54; 18,98</t>
+          <t>9,02; 18,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,58; 11,49</t>
+          <t>2,27; 11,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,43; 8,63</t>
+          <t>0,31; 8,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,9; 12,92</t>
+          <t>6,84; 12,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,58; 8,41</t>
+          <t>2,37; 8,44</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,38; 8,42</t>
+          <t>2,66; 8,46</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>32,54%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14,27; 82,13</t>
+          <t>10,76; 78,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 64,9</t>
+          <t>1,3; 66,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,42; 85,08</t>
+          <t>14,02; 87,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41,9; 102,73</t>
+          <t>39,62; 99,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,2; 62,69</t>
+          <t>9,98; 59,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,44; 46,19</t>
+          <t>1,61; 47,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,15; 81,63</t>
+          <t>36,61; 80,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>13,77; 52,55</t>
+          <t>12,37; 53,05</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12,82; 53,15</t>
+          <t>13,27; 52,54</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-5,14</t>
+          <t>-2,02</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-1,75</t>
+          <t>-1,66</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-4,21</t>
+          <t>-1,8</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 7,27</t>
+          <t>-0,02; 7,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 0,24</t>
+          <t>-6,69; 0,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,44; -0,17</t>
+          <t>-5,48; 1,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 6,36</t>
+          <t>-2,36; 6,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-8,63; -1,06</t>
+          <t>-8,93; -0,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 2,49</t>
+          <t>-5,43; 2,04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 5,69</t>
+          <t>-0,22; 5,47</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,74; -1,36</t>
+          <t>-6,83; -1,29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-11,17; -0,47</t>
+          <t>-4,37; 0,84</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-26,37%</t>
+          <t>-10,33%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-5,89%</t>
+          <t>-5,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-17,1%</t>
+          <t>-7,32%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 41,35</t>
+          <t>-0,1; 41,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-32,16; 1,59</t>
+          <t>-31,15; 3,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-63,45; -1,41</t>
+          <t>-25,45; 8,96</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 23,38</t>
+          <t>-7,65; 23,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-27,71; -3,82</t>
+          <t>-28,01; -2,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-17,16; 9,62</t>
+          <t>-17,24; 7,56</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 25,03</t>
+          <t>-0,96; 23,42</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-25,77; -5,79</t>
+          <t>-25,93; -5,42</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-44,97; -2,01</t>
+          <t>-16,79; 3,85</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4,23</t>
+          <t>3,5</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,79</t>
+          <t>1,24</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11,41</t>
+          <t>2,37</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 7,6</t>
+          <t>-1,48; 7,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 5,29</t>
+          <t>-3,02; 5,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 9,27</t>
+          <t>-1,45; 7,86</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,17; 9,66</t>
+          <t>0,21; 9,67</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 5,17</t>
+          <t>-3,39; 5,53</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 45,67</t>
+          <t>-2,89; 5,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,04; 7,49</t>
+          <t>0,93; 7,31</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 4,04</t>
+          <t>-2,14; 4,29</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,94; 36,13</t>
+          <t>-0,6; 5,4</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>52,54%</t>
+          <t>10,94%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 49,55</t>
+          <t>-8,05; 48,14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-13,98; 35,4</t>
+          <t>-15,15; 40,18</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 58,9</t>
+          <t>-7,17; 53,33</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,12; 40,57</t>
+          <t>0,71; 41,26</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-13,8; 22,35</t>
+          <t>-12,48; 23,68</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-9,26; 180,6</t>
+          <t>-10,59; 25,16</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,67; 37,21</t>
+          <t>3,89; 36,7</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-9,22; 20,05</t>
+          <t>-9,35; 21,36</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,45; 179,78</t>
+          <t>-2,52; 26,96</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-2,38</t>
+          <t>-1,69</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,23</t>
+          <t>1,69</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-1,12</t>
+          <t>0,14</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 6,81</t>
+          <t>-1,07; 6,63</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 4,04</t>
+          <t>-3,25; 4,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,07; 1,33</t>
+          <t>-5,31; 1,7</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,83; 10,18</t>
+          <t>1,7; 9,91</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 4,89</t>
+          <t>-3,7; 4,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 3,81</t>
+          <t>-1,98; 5,15</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,76; 7,31</t>
+          <t>1,61; 7,13</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 3,15</t>
+          <t>-2,13; 3,12</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 1,8</t>
+          <t>-2,25; 2,81</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-10,82%</t>
+          <t>-7,66%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-0,82%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-4,43%</t>
+          <t>0,54%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 33,38</t>
+          <t>-4,51; 32,68</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-14,14; 20,17</t>
+          <t>-13,78; 21,16</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-25,47; 6,58</t>
+          <t>-22,61; 8,16</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,55; 38,67</t>
+          <t>5,55; 37,58</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-10,6; 19,25</t>
+          <t>-12,47; 16,46</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-21,98; 14,23</t>
+          <t>-6,6; 20,45</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,68; 31,01</t>
+          <t>6,3; 29,81</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-9,82; 13,25</t>
+          <t>-8,0; 13,37</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-16,99; 7,5</t>
+          <t>-8,56; 11,81</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-0,27</t>
+          <t>1,02</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,36</t>
+          <t>1,22</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2,16</t>
+          <t>1,17</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,68; 5,75</t>
+          <t>1,66; 6,01</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 2,25</t>
+          <t>-1,55; 2,23</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 2,21</t>
+          <t>-1,25; 2,92</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,86; 8,42</t>
+          <t>3,96; 8,39</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 2,43</t>
+          <t>-1,91; 2,47</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 18,28</t>
+          <t>-0,8; 3,19</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,38; 6,37</t>
+          <t>3,36; 6,36</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 1,61</t>
+          <t>-1,29; 1,66</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 10,09</t>
+          <t>-0,14; 2,65</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-1,47%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>8,72; 32,61</t>
+          <t>8,57; 33,9</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-8,52; 12,76</t>
+          <t>-7,85; 12,79</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-26,14; 12,46</t>
+          <t>-6,24; 16,8</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>13,92; 32,96</t>
+          <t>14,14; 32,89</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-6,51; 9,52</t>
+          <t>-6,84; 9,75</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 72,14</t>
+          <t>-3,01; 12,41</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,34; 29,08</t>
+          <t>14,25; 28,71</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 7,45</t>
+          <t>-5,5; 7,57</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 45,74</t>
+          <t>-0,61; 12,15</t>
         </is>
       </c>
     </row>
